--- a/task a Hai/đăng ký xe.xlsx
+++ b/task a Hai/đăng ký xe.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User Vinatech.DESKTOP-RJJSEQU\Desktop\task a Hai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF038FFE-811A-496C-828D-1F8B41D965C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DDA5C33-E818-4CAF-9685-9F6A501AE336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22944" yWindow="-108" windowWidth="23232" windowHeight="12552" xr2:uid="{9CC8484D-1F35-4C5B-AD21-38EEAF9A49BF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9CC8484D-1F35-4C5B-AD21-38EEAF9A49BF}"/>
   </bookViews>
   <sheets>
     <sheet name="Tuân (2)" sheetId="2" r:id="rId1"/>
@@ -290,38 +290,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -344,15 +329,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -372,9 +376,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -412,7 +416,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -518,7 +522,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -660,7 +664,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -669,20 +673,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05221CE4-88EF-458D-A746-CA7DE7DF1AF0}">
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="34.140625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" style="4" customWidth="1"/>
-    <col min="4" max="7" width="11.5703125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" style="4" customWidth="1"/>
-    <col min="9" max="9" width="16.5703125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" style="4" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" style="4" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="24.88671875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="34.109375" style="4" customWidth="1"/>
+    <col min="3" max="3" width="10.5546875" style="4" customWidth="1"/>
+    <col min="4" max="7" width="11.5546875" style="4" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="16.5546875" style="4" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" style="4" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" style="4" customWidth="1"/>
+    <col min="12" max="16384" width="9.109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -700,63 +704,63 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="7"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-    </row>
-    <row r="5" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="6"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+    </row>
+    <row r="5" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2"/>
+      <c r="C5" s="27"/>
       <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="4">
         <v>92603005</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="7" t="s">
         <v>7</v>
       </c>
       <c r="H5" s="2" t="s">
@@ -766,7 +770,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -778,18 +782,18 @@
       <c r="E6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
-      <c r="J6" s="10"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="8"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -802,201 +806,201 @@
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11" t="s">
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11" t="s">
+      <c r="G8" s="23"/>
+      <c r="H8" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="K8" s="11" t="s">
+      <c r="K8" s="23" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="13" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-    </row>
-    <row r="10" spans="1:12" s="21" customFormat="1" ht="61.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="B10" s="16" t="s">
+      <c r="H9" s="23"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+    </row>
+    <row r="10" spans="1:12" s="16" customFormat="1" ht="61.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10"/>
+      <c r="B10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17">
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12">
         <v>24</v>
       </c>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="20"/>
-    </row>
-    <row r="11" spans="1:12" s="21" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
-      <c r="B11" s="16" t="s">
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="15"/>
+    </row>
+    <row r="11" spans="1:12" s="16" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17">
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12">
         <v>24</v>
       </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="20"/>
-    </row>
-    <row r="12" spans="1:12" s="21" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
-      <c r="B12" s="16" t="s">
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="15"/>
+    </row>
+    <row r="12" spans="1:12" s="16" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17">
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12">
         <v>24</v>
       </c>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="20"/>
-    </row>
-    <row r="13" spans="1:12" s="21" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A13" s="15"/>
-      <c r="B13" s="16" t="s">
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="15"/>
+    </row>
+    <row r="13" spans="1:12" s="16" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="10"/>
+      <c r="B13" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17">
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12">
         <v>24</v>
       </c>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="20"/>
-    </row>
-    <row r="14" spans="1:12" s="21" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A14" s="15"/>
-      <c r="B14" s="16" t="s">
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="15"/>
+    </row>
+    <row r="14" spans="1:12" s="16" customFormat="1" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="10"/>
+      <c r="B14" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17">
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12">
         <v>24</v>
       </c>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="20"/>
-    </row>
-    <row r="15" spans="1:12" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A15" s="15"/>
-      <c r="B15" s="16" t="s">
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="15"/>
+    </row>
+    <row r="15" spans="1:12" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="10"/>
+      <c r="B15" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17">
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12">
         <v>24</v>
       </c>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="17"/>
-      <c r="K15" s="17"/>
-    </row>
-    <row r="16" spans="1:12" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+    </row>
+    <row r="16" spans="1:12" ht="16.2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="23"/>
-      <c r="I16" s="23"/>
-      <c r="J16" s="23"/>
-      <c r="K16" s="23"/>
-    </row>
-    <row r="17" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="G18" s="24" t="s">
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17" spans="2:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="20"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="G18" s="18" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="G19" s="25" t="s">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="G19" s="19" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1022,7 +1026,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{656958DC-2552-4F85-841A-23B0241F1BC4}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
